--- a/backend/data/financials_by_company/1007.HK.xlsx
+++ b/backend/data/financials_by_company/1007.HK.xlsx
@@ -682,152 +682,160 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>11412.600371</v>
+        <v>503250</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001853</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1175000</v>
+        <v>20018000</v>
       </c>
       <c r="E2" t="n">
-        <v>6159000</v>
+        <v>2013000</v>
       </c>
       <c r="F2" t="n">
-        <v>6159000</v>
+        <v>2013000</v>
       </c>
       <c r="G2" t="n">
-        <v>-14355000</v>
+        <v>-33954000</v>
       </c>
       <c r="H2" t="n">
-        <v>11294000</v>
+        <v>29818000</v>
       </c>
       <c r="I2" t="n">
-        <v>65721000</v>
+        <v>116547000</v>
       </c>
       <c r="J2" t="n">
-        <v>7334000</v>
+        <v>22031000</v>
       </c>
       <c r="K2" t="n">
-        <v>-10707000</v>
+        <v>-29574000</v>
       </c>
       <c r="L2" t="n">
-        <v>-3849000</v>
+        <v>-3595000</v>
       </c>
       <c r="M2" t="n">
-        <v>3864000</v>
+        <v>3603000</v>
       </c>
       <c r="N2" t="n">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="O2" t="n">
-        <v>-20502587.399629</v>
+        <v>-35463750</v>
       </c>
       <c r="P2" t="n">
-        <v>-14355000</v>
+        <v>-33954000</v>
       </c>
       <c r="Q2" t="n">
-        <v>100315000</v>
+        <v>199288000</v>
       </c>
       <c r="R2" t="n">
-        <v>6315000</v>
+        <v>13548000</v>
       </c>
       <c r="S2" t="n">
-        <v>-10722000</v>
+        <v>-29582000</v>
       </c>
       <c r="T2" t="n">
-        <v>100587278</v>
+        <v>61714821</v>
       </c>
       <c r="U2" t="n">
-        <v>100587278</v>
+        <v>61714821</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.143</v>
+        <v>-0.55</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.143</v>
+        <v>-0.55</v>
       </c>
       <c r="X2" t="n">
-        <v>-14355000</v>
+        <v>-33954000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-14355000</v>
+        <v>-33954000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-14355000</v>
+        <v>-33954000</v>
       </c>
       <c r="AB2" t="n">
-        <v>189000</v>
+        <v>291000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-14544000</v>
+        <v>-34245000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-14544000</v>
+        <v>-34245000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-27000</v>
+        <v>1068000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-14571000</v>
+        <v>-33177000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1161000</v>
+        <v>4810000</v>
       </c>
       <c r="AH2" t="n">
-        <v>6159000</v>
+        <v>2013000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-6159000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>-2013000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21787000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>-3849000</v>
+        <v>-3595000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3864000</v>
+        <v>3603000</v>
       </c>
       <c r="AM2" t="n">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-18042000</v>
+        <v>-36405000</v>
       </c>
       <c r="AO2" t="n">
-        <v>34594000</v>
+        <v>82741000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10238000</v>
+        <v>18607000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18041000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>51605000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>18041000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>51605000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4078000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4078000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>6315000</v>
+        <v>13548000</v>
       </c>
       <c r="AW2" t="n">
-        <v>16552000</v>
+        <v>46336000</v>
       </c>
       <c r="AX2" t="n">
-        <v>65721000</v>
+        <v>116547000</v>
       </c>
       <c r="AY2" t="n">
-        <v>82273000</v>
+        <v>162883000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>82273000</v>
+        <v>162883000</v>
       </c>
     </row>
     <row r="3">
@@ -986,160 +994,152 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>503250</v>
+        <v>11412.600371</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.001853</v>
       </c>
       <c r="D4" t="n">
-        <v>20018000</v>
+        <v>1175000</v>
       </c>
       <c r="E4" t="n">
-        <v>2013000</v>
+        <v>6159000</v>
       </c>
       <c r="F4" t="n">
-        <v>2013000</v>
+        <v>6159000</v>
       </c>
       <c r="G4" t="n">
-        <v>-33954000</v>
+        <v>-14355000</v>
       </c>
       <c r="H4" t="n">
-        <v>29818000</v>
+        <v>11294000</v>
       </c>
       <c r="I4" t="n">
-        <v>116547000</v>
+        <v>65721000</v>
       </c>
       <c r="J4" t="n">
-        <v>22031000</v>
+        <v>7334000</v>
       </c>
       <c r="K4" t="n">
-        <v>-29574000</v>
+        <v>-10707000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3595000</v>
+        <v>-3849000</v>
       </c>
       <c r="M4" t="n">
-        <v>3603000</v>
+        <v>3864000</v>
       </c>
       <c r="N4" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="O4" t="n">
-        <v>-35463750</v>
+        <v>-20502587.399629</v>
       </c>
       <c r="P4" t="n">
-        <v>-33954000</v>
+        <v>-14355000</v>
       </c>
       <c r="Q4" t="n">
-        <v>199288000</v>
+        <v>100315000</v>
       </c>
       <c r="R4" t="n">
-        <v>13548000</v>
+        <v>6315000</v>
       </c>
       <c r="S4" t="n">
-        <v>-29582000</v>
+        <v>-10722000</v>
       </c>
       <c r="T4" t="n">
-        <v>61714821</v>
+        <v>100587278</v>
       </c>
       <c r="U4" t="n">
-        <v>61714821</v>
+        <v>100587278</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.55</v>
+        <v>-0.143</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.55</v>
+        <v>-0.143</v>
       </c>
       <c r="X4" t="n">
-        <v>-33954000</v>
+        <v>-14355000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-33954000</v>
+        <v>-14355000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-33954000</v>
+        <v>-14355000</v>
       </c>
       <c r="AB4" t="n">
-        <v>291000</v>
+        <v>189000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-34245000</v>
+        <v>-14544000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-34245000</v>
+        <v>-14544000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1068000</v>
+        <v>-27000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-33177000</v>
+        <v>-14571000</v>
       </c>
       <c r="AG4" t="n">
-        <v>4810000</v>
+        <v>1161000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2013000</v>
+        <v>6159000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2013000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>21787000</v>
-      </c>
+        <v>-6159000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-3595000</v>
+        <v>-3849000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3603000</v>
+        <v>3864000</v>
       </c>
       <c r="AM4" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-36405000</v>
+        <v>-18042000</v>
       </c>
       <c r="AO4" t="n">
-        <v>82741000</v>
+        <v>34594000</v>
       </c>
       <c r="AP4" t="n">
-        <v>18607000</v>
+        <v>10238000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>51605000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4000</v>
-      </c>
+        <v>18041000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>51605000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4078000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4078000</v>
-      </c>
+        <v>18041000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>13548000</v>
+        <v>6315000</v>
       </c>
       <c r="AW4" t="n">
-        <v>46336000</v>
+        <v>16552000</v>
       </c>
       <c r="AX4" t="n">
-        <v>116547000</v>
+        <v>65721000</v>
       </c>
       <c r="AY4" t="n">
-        <v>162883000</v>
+        <v>82273000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>162883000</v>
+        <v>82273000</v>
       </c>
     </row>
   </sheetData>
@@ -1455,172 +1455,180 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>105372867</v>
+        <v>68197544</v>
       </c>
       <c r="C2" t="n">
-        <v>105372867</v>
+        <v>68197544</v>
       </c>
       <c r="D2" t="n">
-        <v>72000</v>
+        <v>5782000</v>
       </c>
       <c r="E2" t="n">
-        <v>32424000</v>
+        <v>37931000</v>
       </c>
       <c r="F2" t="n">
-        <v>-188491000</v>
+        <v>-137044000</v>
       </c>
       <c r="G2" t="n">
-        <v>-185491000</v>
+        <v>-129066000</v>
       </c>
       <c r="H2" t="n">
-        <v>-192536000</v>
+        <v>-168224000</v>
       </c>
       <c r="I2" t="n">
-        <v>-188491000</v>
+        <v>-137044000</v>
       </c>
       <c r="J2" t="n">
-        <v>29424000</v>
+        <v>29953000</v>
       </c>
       <c r="K2" t="n">
-        <v>-188491000</v>
+        <v>-137044000</v>
       </c>
       <c r="L2" t="n">
-        <v>-188491000</v>
+        <v>-133866000</v>
       </c>
       <c r="M2" t="n">
-        <v>-190702000</v>
+        <v>-138681000</v>
       </c>
       <c r="N2" t="n">
-        <v>-2211000</v>
+        <v>-1637000</v>
       </c>
       <c r="O2" t="n">
-        <v>-188491000</v>
+        <v>-137044000</v>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>-722493000</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>642157000</v>
+        <v>610342000</v>
       </c>
       <c r="S2" t="n">
-        <v>358000</v>
+        <v>230000</v>
       </c>
       <c r="T2" t="n">
-        <v>358000</v>
+        <v>230000</v>
       </c>
       <c r="U2" t="n">
-        <v>236103000</v>
+        <v>229204000</v>
       </c>
       <c r="V2" t="n">
-        <v>17828000</v>
+        <v>18451000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="X2" t="n">
-        <v>17828000</v>
+        <v>18376000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17828000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>15198000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3178000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>218275000</v>
+        <v>210753000</v>
       </c>
       <c r="AB2" t="n">
-        <v>14596000</v>
+        <v>19555000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11596000</v>
+        <v>14755000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3000000</v>
+        <v>4800000</v>
       </c>
       <c r="AE2" t="n">
-        <v>96429000</v>
+        <v>84171000</v>
       </c>
       <c r="AF2" t="n">
-        <v>68536000</v>
+        <v>52936000</v>
       </c>
       <c r="AG2" t="n">
-        <v>4000</v>
+        <v>1684000</v>
       </c>
       <c r="AH2" t="n">
-        <v>27889000</v>
+        <v>29551000</v>
       </c>
       <c r="AI2" t="n">
-        <v>45401000</v>
+        <v>90523000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19662000</v>
+        <v>47994000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3416000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>6889000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>24333000</v>
+      </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>16246000</v>
+        <v>16772000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-127226000</v>
+        <v>-143448000</v>
       </c>
       <c r="AP2" t="n">
-        <v>143472000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>160220000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AR2" t="n">
-        <v>1349000</v>
+        <v>16772000</v>
       </c>
       <c r="AS2" t="n">
-        <v>22400000</v>
+        <v>31591000</v>
       </c>
       <c r="AT2" t="n">
-        <v>119723000</v>
+        <v>128629000</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>25739000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>42529000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5049000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>13645000</v>
+        <v>12658000</v>
       </c>
       <c r="AY2" t="n">
-        <v>13157000</v>
+        <v>12051000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>488000</v>
+        <v>607000</v>
       </c>
       <c r="BA2" t="n">
-        <v>7800000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>-194000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>19937000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>1366000</v>
+        <v>2883000</v>
       </c>
       <c r="BD2" t="n">
-        <v>-2759000</v>
+        <v>-2207000</v>
       </c>
       <c r="BE2" t="n">
-        <v>4125000</v>
+        <v>5090000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2928000</v>
+        <v>2196000</v>
       </c>
       <c r="BG2" t="n">
-        <v>2928000</v>
+        <v>2196000</v>
       </c>
       <c r="BH2" t="n">
-        <v>2928000</v>
+        <v>2196000</v>
       </c>
     </row>
     <row r="3">
@@ -1807,180 +1815,172 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>68197544</v>
+        <v>105372867</v>
       </c>
       <c r="C4" t="n">
-        <v>68197544</v>
+        <v>105372867</v>
       </c>
       <c r="D4" t="n">
-        <v>5782000</v>
+        <v>72000</v>
       </c>
       <c r="E4" t="n">
-        <v>37931000</v>
+        <v>32424000</v>
       </c>
       <c r="F4" t="n">
-        <v>-137044000</v>
+        <v>-188491000</v>
       </c>
       <c r="G4" t="n">
-        <v>-129066000</v>
+        <v>-185491000</v>
       </c>
       <c r="H4" t="n">
-        <v>-168224000</v>
+        <v>-192536000</v>
       </c>
       <c r="I4" t="n">
-        <v>-137044000</v>
+        <v>-188491000</v>
       </c>
       <c r="J4" t="n">
-        <v>29953000</v>
+        <v>29424000</v>
       </c>
       <c r="K4" t="n">
-        <v>-137044000</v>
+        <v>-188491000</v>
       </c>
       <c r="L4" t="n">
-        <v>-133866000</v>
+        <v>-188491000</v>
       </c>
       <c r="M4" t="n">
-        <v>-138681000</v>
+        <v>-190702000</v>
       </c>
       <c r="N4" t="n">
-        <v>-1637000</v>
+        <v>-2211000</v>
       </c>
       <c r="O4" t="n">
-        <v>-137044000</v>
+        <v>-188491000</v>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>-722493000</v>
+      </c>
       <c r="R4" t="n">
-        <v>610342000</v>
+        <v>642157000</v>
       </c>
       <c r="S4" t="n">
-        <v>230000</v>
+        <v>358000</v>
       </c>
       <c r="T4" t="n">
-        <v>230000</v>
+        <v>358000</v>
       </c>
       <c r="U4" t="n">
-        <v>229204000</v>
+        <v>236103000</v>
       </c>
       <c r="V4" t="n">
-        <v>18451000</v>
+        <v>17828000</v>
       </c>
       <c r="W4" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>18376000</v>
+        <v>17828000</v>
       </c>
       <c r="Y4" t="n">
-        <v>15198000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3178000</v>
-      </c>
+        <v>17828000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>210753000</v>
+        <v>218275000</v>
       </c>
       <c r="AB4" t="n">
-        <v>19555000</v>
+        <v>14596000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14755000</v>
+        <v>11596000</v>
       </c>
       <c r="AD4" t="n">
-        <v>4800000</v>
+        <v>3000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>84171000</v>
+        <v>96429000</v>
       </c>
       <c r="AF4" t="n">
-        <v>52936000</v>
+        <v>68536000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1684000</v>
+        <v>4000</v>
       </c>
       <c r="AH4" t="n">
-        <v>29551000</v>
+        <v>27889000</v>
       </c>
       <c r="AI4" t="n">
-        <v>90523000</v>
+        <v>45401000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>47994000</v>
+        <v>19662000</v>
       </c>
       <c r="AK4" t="n">
-        <v>6889000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>24333000</v>
-      </c>
+        <v>3416000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>16772000</v>
+        <v>16246000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-143448000</v>
+        <v>-127226000</v>
       </c>
       <c r="AP4" t="n">
-        <v>160220000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
+        <v>143472000</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>16772000</v>
+        <v>1349000</v>
       </c>
       <c r="AS4" t="n">
-        <v>31591000</v>
+        <v>22400000</v>
       </c>
       <c r="AT4" t="n">
-        <v>128629000</v>
+        <v>119723000</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>42529000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5049000</v>
-      </c>
+        <v>25739000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>12658000</v>
+        <v>13645000</v>
       </c>
       <c r="AY4" t="n">
-        <v>12051000</v>
+        <v>13157000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>607000</v>
+        <v>488000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-194000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>19937000</v>
-      </c>
+        <v>7800000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>2883000</v>
+        <v>1366000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-2207000</v>
+        <v>-2759000</v>
       </c>
       <c r="BE4" t="n">
-        <v>5090000</v>
+        <v>4125000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2196000</v>
+        <v>2928000</v>
       </c>
       <c r="BG4" t="n">
-        <v>2196000</v>
+        <v>2928000</v>
       </c>
       <c r="BH4" t="n">
-        <v>2196000</v>
+        <v>2928000</v>
       </c>
     </row>
   </sheetData>
@@ -2206,126 +2206,128 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>9091000</v>
+        <v>-7518000</v>
       </c>
       <c r="C2" t="n">
-        <v>-9131000</v>
+        <v>-25591000</v>
       </c>
       <c r="D2" t="n">
-        <v>14970000</v>
+        <v>15047000</v>
       </c>
       <c r="E2" t="n">
-        <v>5150000</v>
+        <v>41623000</v>
       </c>
       <c r="F2" t="n">
-        <v>-306000</v>
+        <v>-5852000</v>
       </c>
       <c r="G2" t="n">
-        <v>2928000</v>
+        <v>2196000</v>
       </c>
       <c r="H2" t="n">
-        <v>1701000</v>
+        <v>3177000</v>
       </c>
       <c r="I2" t="n">
-        <v>9000</v>
+        <v>-55000</v>
       </c>
       <c r="J2" t="n">
-        <v>1218000</v>
+        <v>-926000</v>
       </c>
       <c r="K2" t="n">
-        <v>-8032000</v>
+        <v>2256000</v>
       </c>
       <c r="L2" t="n">
-        <v>-185000</v>
+        <v>-142000</v>
       </c>
       <c r="M2" t="n">
-        <v>5150000</v>
+        <v>41623000</v>
       </c>
       <c r="N2" t="n">
-        <v>5150000</v>
+        <v>41623000</v>
       </c>
       <c r="O2" t="n">
-        <v>5839000</v>
+        <v>-10544000</v>
       </c>
       <c r="P2" t="n">
-        <v>13339000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1631000</v>
-      </c>
+        <v>15047000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>14970000</v>
+        <v>15047000</v>
       </c>
       <c r="S2" t="n">
-        <v>-7500000</v>
+        <v>-25591000</v>
       </c>
       <c r="T2" t="n">
-        <v>-7500000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>-25591000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>15047000</v>
+      </c>
       <c r="V2" t="n">
-        <v>-147000</v>
+        <v>-1516000</v>
       </c>
       <c r="W2" t="n">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="X2" t="n">
-        <v>-162000</v>
+        <v>-1524000</v>
       </c>
       <c r="Y2" t="n">
-        <v>144000</v>
+        <v>4328000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-306000</v>
+        <v>-5852000</v>
       </c>
       <c r="AA2" t="n">
-        <v>9397000</v>
+        <v>-1666000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>785000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7970000</v>
+        <v>-20177000</v>
       </c>
       <c r="AD2" t="n">
-        <v>553000</v>
+        <v>-2457000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1789000</v>
+        <v>-33317000</v>
       </c>
       <c r="AF2" t="n">
-        <v>3836000</v>
+        <v>14114000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1443000</v>
+        <v>1428000</v>
       </c>
       <c r="AH2" t="n">
-        <v>349000</v>
+        <v>55000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2166000</v>
+        <v>-2121000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3199000</v>
       </c>
       <c r="AK2" t="n">
-        <v>267000</v>
+        <v>-1575000</v>
       </c>
       <c r="AL2" t="n">
-        <v>11294000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>29818000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>4000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>11294000</v>
+        <v>29814000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-144000</v>
+        <v>-205000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-14571000</v>
+        <v>-33177000</v>
       </c>
     </row>
     <row r="3">
@@ -2458,128 +2460,126 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-7518000</v>
+        <v>9091000</v>
       </c>
       <c r="C4" t="n">
-        <v>-25591000</v>
+        <v>-9131000</v>
       </c>
       <c r="D4" t="n">
-        <v>15047000</v>
+        <v>14970000</v>
       </c>
       <c r="E4" t="n">
-        <v>41623000</v>
+        <v>5150000</v>
       </c>
       <c r="F4" t="n">
-        <v>-5852000</v>
+        <v>-306000</v>
       </c>
       <c r="G4" t="n">
-        <v>2196000</v>
+        <v>2928000</v>
       </c>
       <c r="H4" t="n">
-        <v>3177000</v>
+        <v>1701000</v>
       </c>
       <c r="I4" t="n">
-        <v>-55000</v>
+        <v>9000</v>
       </c>
       <c r="J4" t="n">
-        <v>-926000</v>
+        <v>1218000</v>
       </c>
       <c r="K4" t="n">
-        <v>2256000</v>
+        <v>-8032000</v>
       </c>
       <c r="L4" t="n">
-        <v>-142000</v>
+        <v>-185000</v>
       </c>
       <c r="M4" t="n">
-        <v>41623000</v>
+        <v>5150000</v>
       </c>
       <c r="N4" t="n">
-        <v>41623000</v>
+        <v>5150000</v>
       </c>
       <c r="O4" t="n">
-        <v>-10544000</v>
+        <v>5839000</v>
       </c>
       <c r="P4" t="n">
-        <v>15047000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>13339000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1631000</v>
+      </c>
       <c r="R4" t="n">
-        <v>15047000</v>
+        <v>14970000</v>
       </c>
       <c r="S4" t="n">
-        <v>-25591000</v>
+        <v>-7500000</v>
       </c>
       <c r="T4" t="n">
-        <v>-25591000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>15047000</v>
-      </c>
+        <v>-7500000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-1516000</v>
+        <v>-147000</v>
       </c>
       <c r="W4" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="X4" t="n">
-        <v>-1524000</v>
+        <v>-162000</v>
       </c>
       <c r="Y4" t="n">
-        <v>4328000</v>
+        <v>144000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-5852000</v>
+        <v>-306000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1666000</v>
+        <v>9397000</v>
       </c>
       <c r="AB4" t="n">
-        <v>785000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-20177000</v>
+        <v>7970000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2457000</v>
+        <v>553000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-33317000</v>
+        <v>1789000</v>
       </c>
       <c r="AF4" t="n">
-        <v>14114000</v>
+        <v>3836000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1428000</v>
+        <v>1443000</v>
       </c>
       <c r="AH4" t="n">
-        <v>55000</v>
+        <v>349000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2121000</v>
+        <v>-2166000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3199000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1575000</v>
+        <v>267000</v>
       </c>
       <c r="AL4" t="n">
-        <v>29818000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>4000</v>
-      </c>
+        <v>11294000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>29814000</v>
+        <v>11294000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-205000</v>
+        <v>-144000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-33177000</v>
+        <v>-14571000</v>
       </c>
     </row>
   </sheetData>
@@ -3094,182 +3094,182 @@
       </c>
       <c r="CV1" t="inlineStr">
         <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Shui Chak  Hung', 'age': 54, 'title': 'Executive Chairman', 'yearBorn': 1971, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kam Chuen  So', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2023, 'totalPay': 2430410, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mingjie  Yuan', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2023, 'totalPay': 755304, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jia  Bi', 'age': 44, 'title': 'Public Affair Manager', 'yearBorn': 1981, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming  Zhang', 'age': 42, 'title': 'Marketing Director', 'yearBorn': 1983, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Kit  Wong', 'age': 54, 'title': 'Company Secretary', 'yearBorn': 1971, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Shui Chak  Hung', 'age': 54, 'title': 'Executive Chairman', 'yearBorn': 1971, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kam Chuen  So', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2023, 'totalPay': 2428473, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mingjie  Yuan', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2023, 'totalPay': 754702, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Jia  Bi', 'age': 44, 'title': 'Public Affair Manager', 'yearBorn': 1981, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming  Zhang', 'age': 42, 'title': 'Marketing Director', 'yearBorn': 1983, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Kit  Wong', 'age': 54, 'title': 'Company Secretary', 'yearBorn': 1971, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.066</v>
+        <v>-0.092</v>
       </c>
       <c r="AD2" t="n">
         <v>752000</v>
@@ -3486,7 +3486,7 @@
         <v>189592867</v>
       </c>
       <c r="BG2" t="n">
-        <v>-1.1604581</v>
+        <v>-1.1599625</v>
       </c>
       <c r="BH2" t="n">
         <v>1703980800</v>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -3630,45 +3630,45 @@
       <c r="CU2" t="n">
         <v>1743144993</v>
       </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+      <c r="CV2" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
+          <t>LONGHUI INTL</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Longhui International Holdings Limited</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>finmb_574417809</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DA2" t="n">
+      <c r="DC2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Longhui International Holdings Limited</t>
         </is>
       </c>
       <c r="DE2" t="b">
@@ -3678,66 +3678,64 @@
         <v>-5.4054065</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>LONGHUI INTL</t>
-        </is>
+        <v>-0.15</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.6</v>
       </c>
       <c r="DI2" t="n">
+        <v>-0.8955224000000001</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.8955224000000001</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.06034678</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1288229400000</v>
+      </c>
+      <c r="DR2" t="n">
         <v>-0.0040000007</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>0.066 - 0.07</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DU2" t="n">
         <v>0</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="DV2" t="n">
         <v>0.0040000007</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DW2" t="n">
         <v>0.06060607</v>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>0.066 - 0.67</t>
         </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.8955224000000001</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1725024063</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1725024063</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.8955224000000001</v>
       </c>
       <c r="DY2" t="n">
         <v>-0.6</v>
@@ -3746,19 +3744,21 @@
         <v>-0.8955224000000001</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.060321007</v>
+        <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>15</v>
+        <v>1725024063</v>
       </c>
       <c r="EC2" t="n">
-        <v>15</v>
+        <v>1725024063</v>
       </c>
       <c r="ED2" t="b">
         <v>0</v>
       </c>
-      <c r="EE2" t="n">
-        <v>1288229400000</v>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
